--- a/Team-Data/2007-08/2-27-2007-08.xlsx
+++ b/Team-Data/2007-08/2-27-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,22 +728,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" t="n">
         <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.429</v>
+        <v>0.418</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
         <v>79.3</v>
@@ -685,34 +752,34 @@
         <v>0.442</v>
       </c>
       <c r="L2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>11.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.342</v>
+        <v>0.339</v>
       </c>
       <c r="O2" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.776</v>
+        <v>0.773</v>
       </c>
       <c r="R2" t="n">
         <v>12.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T2" t="n">
         <v>42.4</v>
       </c>
       <c r="U2" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V2" t="n">
         <v>15.6</v>
@@ -724,22 +791,22 @@
         <v>5.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.5</v>
+        <v>95</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.3</v>
+        <v>-2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
@@ -754,7 +821,7 @@
         <v>4</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -769,13 +836,13 @@
         <v>29</v>
       </c>
       <c r="AN2" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AO2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ2" t="n">
         <v>7</v>
@@ -784,13 +851,13 @@
         <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV2" t="n">
         <v>25</v>
@@ -802,7 +869,7 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ2" t="n">
         <v>18</v>
@@ -811,7 +878,7 @@
         <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC2" t="n">
         <v>19</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.786</v>
+        <v>0.782</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
@@ -861,19 +928,19 @@
         <v>35.9</v>
       </c>
       <c r="J3" t="n">
-        <v>75.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="K3" t="n">
-        <v>0.475</v>
+        <v>0.474</v>
       </c>
       <c r="L3" t="n">
         <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="O3" t="n">
         <v>20.9</v>
@@ -882,25 +949,25 @@
         <v>27.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R3" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S3" t="n">
         <v>31.2</v>
       </c>
       <c r="T3" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U3" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V3" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W3" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X3" t="n">
         <v>4.4</v>
@@ -909,19 +976,19 @@
         <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA3" t="n">
         <v>23.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.2</v>
+        <v>100.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
         <v>22</v>
@@ -957,7 +1024,7 @@
         <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -975,13 +1042,13 @@
         <v>11</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -1025,34 +1092,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" t="n">
         <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
         <v>6.1</v>
       </c>
       <c r="M4" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="N4" t="n">
         <v>0.355</v>
@@ -1070,16 +1137,16 @@
         <v>11.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T4" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U4" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V4" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W4" t="n">
         <v>7.4</v>
@@ -1088,22 +1155,22 @@
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA4" t="n">
         <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.9</v>
+        <v>-5.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
@@ -1121,7 +1188,7 @@
         <v>24</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK4" t="n">
         <v>20</v>
@@ -1130,7 +1197,7 @@
         <v>17</v>
       </c>
       <c r="AM4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN4" t="n">
         <v>15</v>
@@ -1142,25 +1209,25 @@
         <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR4" t="n">
         <v>18</v>
       </c>
       <c r="AS4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT4" t="n">
         <v>26</v>
       </c>
-      <c r="AT4" t="n">
-        <v>25</v>
-      </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV4" t="n">
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1169,16 +1236,16 @@
         <v>30</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA4" t="n">
         <v>17</v>
       </c>
       <c r="BB4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC4" t="n">
         <v>24</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>26</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -1207,85 +1274,85 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
         <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>0.404</v>
+        <v>0.393</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J5" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.428</v>
+        <v>0.427</v>
       </c>
       <c r="L5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M5" t="n">
         <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.352</v>
+        <v>0.348</v>
       </c>
       <c r="O5" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.742</v>
+        <v>0.746</v>
       </c>
       <c r="R5" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="S5" t="n">
         <v>30.2</v>
       </c>
       <c r="T5" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V5" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W5" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1309,13 +1376,13 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>17</v>
@@ -1336,13 +1403,13 @@
         <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>13</v>
@@ -1351,10 +1418,10 @@
         <v>28</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
         <v>32</v>
       </c>
       <c r="F6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>0.552</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1410,7 +1477,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L6" t="n">
         <v>6.9</v>
@@ -1419,7 +1486,7 @@
         <v>19.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O6" t="n">
         <v>17.9</v>
@@ -1428,19 +1495,19 @@
         <v>24.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R6" t="n">
         <v>12.9</v>
       </c>
       <c r="S6" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T6" t="n">
         <v>44.2</v>
       </c>
       <c r="U6" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V6" t="n">
         <v>14.4</v>
@@ -1458,13 +1525,13 @@
         <v>21.9</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>97.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="AD6" t="n">
         <v>2</v>
@@ -1482,13 +1549,13 @@
         <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
         <v>10</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>11</v>
@@ -1497,7 +1564,7 @@
         <v>12</v>
       </c>
       <c r="AN6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO6" t="n">
         <v>22</v>
@@ -1521,7 +1588,7 @@
         <v>26</v>
       </c>
       <c r="AV6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
         <v>13</v>
@@ -1536,13 +1603,13 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
         <v>16</v>
       </c>
       <c r="BC6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG7" t="n">
         <v>7</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
         <v>9</v>
@@ -1718,7 +1785,7 @@
         <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -1753,91 +1820,91 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>0.596</v>
+        <v>0.589</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
       </c>
       <c r="I8" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
       <c r="J8" t="n">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.457</v>
+        <v>0.453</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
         <v>18.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="O8" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="P8" t="n">
-        <v>30.4</v>
+        <v>30.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.758</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S8" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T8" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
         <v>15.4</v>
       </c>
       <c r="W8" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>7.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="AB8" t="n">
-        <v>107.6</v>
+        <v>107</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -1849,19 +1916,19 @@
         <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS8" t="n">
         <v>3</v>
@@ -1882,10 +1949,10 @@
         <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" t="n">
         <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.724</v>
+        <v>0.737</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J9" t="n">
-        <v>80</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L9" t="n">
         <v>6.1</v>
@@ -1965,13 +2032,13 @@
         <v>16.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O9" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P9" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0.762</v>
@@ -1986,7 +2053,7 @@
         <v>41.2</v>
       </c>
       <c r="U9" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V9" t="n">
         <v>11.5</v>
@@ -2007,10 +2074,10 @@
         <v>20.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>2</v>
@@ -2025,16 +2092,16 @@
         <v>2</v>
       </c>
       <c r="AH9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL9" t="n">
         <v>18</v>
@@ -2043,7 +2110,7 @@
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
@@ -2058,7 +2125,7 @@
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
@@ -2070,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2225,7 +2292,7 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>13</v>
@@ -2237,10 +2304,10 @@
         <v>19</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>12</v>
@@ -2252,13 +2319,13 @@
         <v>8</v>
       </c>
       <c r="AW10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>27</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>4.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
@@ -2407,7 +2474,7 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
@@ -2416,13 +2483,13 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>3</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E12" t="n">
         <v>22</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>0.379</v>
+        <v>0.386</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J12" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K12" t="n">
         <v>0.438</v>
@@ -2508,16 +2575,16 @@
         <v>8.9</v>
       </c>
       <c r="M12" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N12" t="n">
         <v>0.364</v>
       </c>
       <c r="O12" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P12" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="Q12" t="n">
         <v>0.77</v>
@@ -2529,46 +2596,46 @@
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.6</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
         <v>22.8</v>
       </c>
       <c r="V12" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X12" t="n">
         <v>5.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.4</v>
+        <v>102.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
       </c>
       <c r="AE12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF12" t="n">
         <v>22</v>
       </c>
-      <c r="AF12" t="n">
-        <v>23</v>
-      </c>
       <c r="AG12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH12" t="n">
         <v>19</v>
@@ -2577,10 +2644,10 @@
         <v>9</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2589,13 +2656,13 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
         <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>9</v>
@@ -2613,13 +2680,13 @@
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2628,7 +2695,7 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2730,37 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
         <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>0.345</v>
+        <v>0.352</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>34.4</v>
+        <v>34.6</v>
       </c>
       <c r="J13" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.437</v>
+        <v>0.44</v>
       </c>
       <c r="L13" t="n">
         <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.333</v>
+        <v>0.334</v>
       </c>
       <c r="O13" t="n">
         <v>21</v>
@@ -2702,10 +2769,10 @@
         <v>26.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R13" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S13" t="n">
         <v>30.9</v>
@@ -2729,25 +2796,25 @@
         <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA13" t="n">
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AC13" t="n">
         <v>-4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
         <v>24</v>
       </c>
       <c r="AF13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>24</v>
@@ -2762,16 +2829,16 @@
         <v>24</v>
       </c>
       <c r="AK13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL13" t="n">
         <v>28</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>27</v>
       </c>
       <c r="AM13" t="n">
         <v>26</v>
       </c>
       <c r="AN13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
         <v>7</v>
@@ -2780,7 +2847,7 @@
         <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>28</v>
@@ -2789,31 +2856,31 @@
         <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX13" t="n">
         <v>10</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AY13" t="n">
         <v>19</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>18</v>
       </c>
       <c r="AZ13" t="n">
         <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>22</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2965,7 +3032,7 @@
         <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS14" t="n">
         <v>2</v>
@@ -2974,7 +3041,7 @@
         <v>5</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV14" t="n">
         <v>16</v>
@@ -2986,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ14" t="n">
         <v>11</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
         <v>28</v>
@@ -3120,16 +3187,16 @@
         <v>13</v>
       </c>
       <c r="AI15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ15" t="n">
         <v>12</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
@@ -3138,7 +3205,7 @@
         <v>14</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>18</v>
@@ -3180,7 +3247,7 @@
         <v>12</v>
       </c>
       <c r="BC15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3302,13 +3369,13 @@
         <v>6</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3347,10 +3414,10 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
@@ -3362,7 +3429,7 @@
         <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>-6.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
         <v>22</v>
@@ -3487,13 +3554,13 @@
         <v>18</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>22</v>
@@ -3511,7 +3578,7 @@
         <v>18</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
@@ -3520,7 +3587,7 @@
         <v>24</v>
       </c>
       <c r="AU17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV17" t="n">
         <v>15</v>
@@ -3541,10 +3608,10 @@
         <v>21</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>0.214</v>
+        <v>0.218</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3591,37 +3658,37 @@
         <v>36.6</v>
       </c>
       <c r="J18" t="n">
-        <v>82.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K18" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L18" t="n">
         <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N18" t="n">
-        <v>0.334</v>
+        <v>0.335</v>
       </c>
       <c r="O18" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P18" t="n">
         <v>20.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.724</v>
+        <v>0.723</v>
       </c>
       <c r="R18" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S18" t="n">
         <v>29.8</v>
       </c>
       <c r="T18" t="n">
-        <v>41.9</v>
+        <v>42.1</v>
       </c>
       <c r="U18" t="n">
         <v>19.3</v>
@@ -3630,7 +3697,7 @@
         <v>15.3</v>
       </c>
       <c r="W18" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X18" t="n">
         <v>3.7</v>
@@ -3639,25 +3706,25 @@
         <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AA18" t="n">
         <v>17.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.5</v>
+        <v>93.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.3</v>
+        <v>-7</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
       </c>
       <c r="AF18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG18" t="n">
         <v>29</v>
@@ -3669,10 +3736,10 @@
         <v>14</v>
       </c>
       <c r="AJ18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>24</v>
@@ -3681,34 +3748,34 @@
         <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
       </c>
       <c r="AP18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU18" t="n">
         <v>27</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-4.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF19" t="n">
         <v>18</v>
       </c>
       <c r="AG19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3860,7 +3927,7 @@
         <v>19</v>
       </c>
       <c r="AM19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN19" t="n">
         <v>18</v>
@@ -3869,13 +3936,13 @@
         <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS19" t="n">
         <v>13</v>
@@ -3890,7 +3957,7 @@
         <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3905,7 +3972,7 @@
         <v>7</v>
       </c>
       <c r="BB19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H20" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J20" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L20" t="n">
         <v>7.8</v>
@@ -3967,25 +4034,25 @@
         <v>20.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.388</v>
+        <v>0.386</v>
       </c>
       <c r="O20" t="n">
         <v>15.5</v>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S20" t="n">
         <v>30.8</v>
       </c>
       <c r="T20" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U20" t="n">
         <v>21.4</v>
@@ -3994,52 +4061,52 @@
         <v>12.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
         <v>3.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.1</v>
+        <v>99.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
         <v>8</v>
       </c>
       <c r="AL20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM20" t="n">
         <v>8</v>
@@ -4057,22 +4124,22 @@
         <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AS20" t="n">
         <v>15</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4087,10 +4154,10 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
         <v>39</v>
       </c>
       <c r="G21" t="n">
-        <v>0.316</v>
+        <v>0.304</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.1</v>
+        <v>34.9</v>
       </c>
       <c r="J21" t="n">
-        <v>79.8</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M21" t="n">
         <v>17.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O21" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P21" t="n">
         <v>26.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.727</v>
+        <v>0.729</v>
       </c>
       <c r="R21" t="n">
         <v>12.2</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T21" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U21" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="V21" t="n">
         <v>15.5</v>
@@ -4179,7 +4246,7 @@
         <v>6.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
         <v>5.3</v>
@@ -4191,13 +4258,13 @@
         <v>21.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.8</v>
+        <v>-6.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4212,25 +4279,25 @@
         <v>8</v>
       </c>
       <c r="AI21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK21" t="n">
         <v>27</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>24</v>
-      </c>
       <c r="AL21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="n">
         <v>15</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP21" t="n">
         <v>10</v>
@@ -4239,10 +4306,10 @@
         <v>22</v>
       </c>
       <c r="AR21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT21" t="n">
         <v>17</v>
@@ -4263,16 +4330,16 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>16</v>
       </c>
       <c r="BB21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" t="n">
         <v>37</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.617</v>
+        <v>0.627</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J22" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.47</v>
+        <v>0.471</v>
       </c>
       <c r="L22" t="n">
         <v>9.300000000000001</v>
@@ -4331,7 +4398,7 @@
         <v>24.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="O22" t="n">
         <v>21.2</v>
@@ -4340,7 +4407,7 @@
         <v>29.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R22" t="n">
         <v>9.699999999999999</v>
@@ -4355,7 +4422,7 @@
         <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W22" t="n">
         <v>6.2</v>
@@ -4373,19 +4440,19 @@
         <v>24</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.1</v>
+        <v>104.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
         <v>10</v>
@@ -4394,7 +4461,7 @@
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4412,7 +4479,7 @@
         <v>6</v>
       </c>
       <c r="AO22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP22" t="n">
         <v>2</v>
@@ -4421,19 +4488,19 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>14</v>
       </c>
       <c r="AU22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW22" t="n">
         <v>27</v>
@@ -4445,7 +4512,7 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
         <v>32</v>
       </c>
       <c r="G23" t="n">
-        <v>0.448</v>
+        <v>0.439</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J23" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K23" t="n">
         <v>0.457</v>
@@ -4513,19 +4580,19 @@
         <v>11.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="O23" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P23" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.705</v>
+        <v>0.703</v>
       </c>
       <c r="R23" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="S23" t="n">
         <v>29.1</v>
@@ -4534,37 +4601,37 @@
         <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W23" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA23" t="n">
         <v>20.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AD23" t="n">
         <v>2</v>
       </c>
       <c r="AE23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF23" t="n">
         <v>18</v>
@@ -4576,13 +4643,13 @@
         <v>19</v>
       </c>
       <c r="AI23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ23" t="n">
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4594,13 +4661,13 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP23" t="n">
         <v>11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR23" t="n">
         <v>2</v>
@@ -4612,7 +4679,7 @@
         <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV23" t="n">
         <v>19</v>
@@ -4621,7 +4688,7 @@
         <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
         <v>15</v>
@@ -4636,7 +4703,7 @@
         <v>25</v>
       </c>
       <c r="BC23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4732,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E24" t="n">
         <v>39</v>
       </c>
       <c r="F24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" t="n">
-        <v>0.672</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="J24" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0.493</v>
@@ -4692,16 +4759,16 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="O24" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q24" t="n">
         <v>0.788</v>
@@ -4713,16 +4780,16 @@
         <v>32.3</v>
       </c>
       <c r="T24" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U24" t="n">
         <v>26.8</v>
       </c>
       <c r="V24" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X24" t="n">
         <v>6.9</v>
@@ -4737,10 +4804,10 @@
         <v>20.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.4</v>
+        <v>109.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AD24" t="n">
         <v>2</v>
@@ -4749,10 +4816,10 @@
         <v>4</v>
       </c>
       <c r="AF24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH24" t="n">
         <v>19</v>
@@ -4776,13 +4843,13 @@
         <v>4</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP24" t="n">
         <v>24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
@@ -4800,7 +4867,7 @@
         <v>9</v>
       </c>
       <c r="AW24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4809,7 +4876,7 @@
         <v>1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
         <v>20</v>
@@ -4818,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25" t="n">
         <v>28</v>
       </c>
       <c r="G25" t="n">
-        <v>0.517</v>
+        <v>0.509</v>
       </c>
       <c r="H25" t="n">
         <v>48.7</v>
       </c>
       <c r="I25" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J25" t="n">
-        <v>78.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.449</v>
@@ -4874,31 +4941,31 @@
         <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="N25" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O25" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P25" t="n">
         <v>23.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.762</v>
+        <v>0.764</v>
       </c>
       <c r="R25" t="n">
         <v>10.6</v>
       </c>
       <c r="S25" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T25" t="n">
         <v>40.2</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V25" t="n">
         <v>13.2</v>
@@ -4916,13 +4983,13 @@
         <v>20</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD25" t="n">
         <v>2</v>
@@ -4940,22 +5007,22 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>16</v>
       </c>
       <c r="AM25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>23</v>
@@ -4964,13 +5031,13 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT25" t="n">
         <v>29</v>
@@ -4988,7 +5055,7 @@
         <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ25" t="n">
         <v>8</v>
@@ -4997,10 +5064,10 @@
         <v>18</v>
       </c>
       <c r="BB25" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BC25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E26" t="n">
         <v>26</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456</v>
+        <v>0.464</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.455</v>
@@ -5059,31 +5126,31 @@
         <v>17.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.374</v>
       </c>
       <c r="O26" t="n">
         <v>21.9</v>
       </c>
       <c r="P26" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.786</v>
+        <v>0.789</v>
       </c>
       <c r="R26" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S26" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T26" t="n">
         <v>40.3</v>
       </c>
       <c r="U26" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V26" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W26" t="n">
         <v>7.9</v>
@@ -5092,49 +5159,49 @@
         <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA26" t="n">
         <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.8</v>
+        <v>100.5</v>
       </c>
       <c r="AC26" t="n">
         <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
         <v>17</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="n">
         <v>21</v>
       </c>
       <c r="AK26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL26" t="n">
         <v>14</v>
       </c>
-      <c r="AL26" t="n">
-        <v>15</v>
-      </c>
       <c r="AM26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN26" t="n">
         <v>9</v>
@@ -5143,19 +5210,19 @@
         <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
@@ -5173,7 +5240,7 @@
         <v>26</v>
       </c>
       <c r="AZ26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>5</v>
@@ -5301,7 +5368,7 @@
         <v>4</v>
       </c>
       <c r="AH27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>23</v>
@@ -5358,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" t="n">
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G28" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,10 +5478,10 @@
         <v>37.6</v>
       </c>
       <c r="J28" t="n">
-        <v>85.59999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.439</v>
+        <v>0.441</v>
       </c>
       <c r="L28" t="n">
         <v>4.2</v>
@@ -5423,7 +5490,7 @@
         <v>12.3</v>
       </c>
       <c r="N28" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O28" t="n">
         <v>17.4</v>
@@ -5432,19 +5499,19 @@
         <v>22.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.764</v>
+        <v>0.762</v>
       </c>
       <c r="R28" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="U28" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="V28" t="n">
         <v>16.2</v>
@@ -5453,25 +5520,25 @@
         <v>6.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB28" t="n">
         <v>96.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7.4</v>
+        <v>-6.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
@@ -5483,25 +5550,25 @@
         <v>27</v>
       </c>
       <c r="AH28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM28" t="n">
         <v>27</v>
       </c>
       <c r="AN28" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO28" t="n">
         <v>24</v>
@@ -5510,10 +5577,10 @@
         <v>25</v>
       </c>
       <c r="AQ28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR28" t="n">
         <v>11</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>7</v>
       </c>
       <c r="AS28" t="n">
         <v>1</v>
@@ -5522,31 +5589,31 @@
         <v>1</v>
       </c>
       <c r="AU28" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV28" t="n">
         <v>29</v>
       </c>
       <c r="AW28" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY28" t="n">
         <v>24</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>25</v>
       </c>
       <c r="AZ28" t="n">
         <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
         <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" t="n">
         <v>24</v>
       </c>
       <c r="G29" t="n">
-        <v>0.571</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5599,37 +5666,37 @@
         <v>0.465</v>
       </c>
       <c r="L29" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M29" t="n">
         <v>18.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.418</v>
+        <v>0.422</v>
       </c>
       <c r="O29" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P29" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="R29" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T29" t="n">
         <v>40.3</v>
       </c>
       <c r="U29" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V29" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="W29" t="n">
         <v>6.9</v>
@@ -5638,25 +5705,25 @@
         <v>4</v>
       </c>
       <c r="Y29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z29" t="n">
         <v>19.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="n">
         <v>13</v>
@@ -5677,7 +5744,7 @@
         <v>6</v>
       </c>
       <c r="AL29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5689,19 +5756,19 @@
         <v>26</v>
       </c>
       <c r="AP29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ29" t="n">
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS29" t="n">
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -5713,7 +5780,7 @@
         <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY29" t="n">
         <v>6</v>
@@ -5725,7 +5792,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC29" t="n">
         <v>8</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -5757,64 +5824,64 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F30" t="n">
         <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>0.638</v>
+        <v>0.632</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="J30" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.492</v>
       </c>
       <c r="L30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="M30" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R30" t="n">
         <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T30" t="n">
         <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="V30" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W30" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>4.4</v>
@@ -5832,13 +5899,13 @@
         <v>105.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF30" t="n">
         <v>9</v>
@@ -5847,13 +5914,13 @@
         <v>9</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5880,7 +5947,7 @@
         <v>15</v>
       </c>
       <c r="AS30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT30" t="n">
         <v>22</v>
@@ -5889,13 +5956,13 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY30" t="n">
         <v>27</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6032,13 +6099,13 @@
         <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
@@ -6047,13 +6114,13 @@
         <v>11</v>
       </c>
       <c r="AN31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>3</v>
@@ -6062,10 +6129,10 @@
         <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
@@ -6092,7 +6159,7 @@
         <v>15</v>
       </c>
       <c r="BC31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-27-2007-08</t>
+          <t>2008-02-27</t>
         </is>
       </c>
     </row>
